--- a/data/freight/GSCPI.xlsx
+++ b/data/freight/GSCPI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\freight\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD580E5-3E82-4BA6-A450-41259D63590B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB03DC8-9625-4DB7-8B33-733A188AC16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EC87154-67AB-4E78-98B9-C9468743549E}"/>
   </bookViews>
@@ -3371,9 +3371,9 @@
   <dimension ref="A1:H348"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="6"/>
     <col min="7" max="7" width="8.88671875" customWidth="1"/>
